--- a/etf_holdings/2026-09-30_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-30_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:40</t>
+          <t>2026-09-30 23:16:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:40</t>
+          <t>2026-09-30 23:16:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:40</t>
+          <t>2026-09-30 23:16:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:42</t>
+          <t>2026-09-30 23:16:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:42</t>
+          <t>2026-09-30 23:16:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:42</t>
+          <t>2026-09-30 23:16:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:42</t>
+          <t>2026-09-30 23:16:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:42</t>
+          <t>2026-09-30 23:16:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:42</t>
+          <t>2026-09-30 23:16:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:44</t>
+          <t>2026-09-30 23:16:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:44</t>
+          <t>2026-09-30 23:16:56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">

--- a/etf_holdings/2026-09-30_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-30_00990A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:52</t>
+          <t>2026-09-30 23:56:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.39%243,000</t>
+          <t>3.16%243,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:52</t>
+          <t>2026-09-30 23:56:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.19%633,000</t>
+          <t>3.08%633,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:52</t>
+          <t>2026-09-30 23:56:33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.65%406,000</t>
+          <t>2.66%406,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:53</t>
+          <t>2026-09-30 23:56:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.79%134,000</t>
+          <t>1.75%134,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:53</t>
+          <t>2026-09-30 23:56:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -756,40 +756,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>6857ADVANTEST CORP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.86%1175</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.62%519,000</t>
+          <t>1.61%88,100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>519000</v>
+        <v>88100</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:53</t>
+          <t>2026-09-30 23:56:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -819,40 +819,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6857ADVANTEST CORP</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.86%1175</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.55%88,100</t>
+          <t>1.60%519,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>88100</v>
+        <v>519000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:53</t>
+          <t>2026-09-30 23:56:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -882,40 +882,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>6981MURATA MANUFACTURING CO LTD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+1.03%3435</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.48%158,000</t>
+          <t>1.53%351,900</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>158000</v>
+        <v>351900</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:53</t>
+          <t>2026-09-30 23:56:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -945,40 +945,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6981MURATA MANUFACTURING CO LTD</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.03%3435</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.46%351,900</t>
+          <t>1.42%158,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>351900</v>
+        <v>158000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:53</t>
+          <t>2026-09-30 23:56:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.37%1,665,000</t>
+          <t>1.30%1,665,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:54</t>
+          <t>2026-09-30 23:56:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.14%348,000</t>
+          <t>1.17%348,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:54</t>
+          <t>2026-09-30 23:56:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4062IBIDEN CO LTD</t>
+          <t>6920LASERTEC CORP</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1154,16 +1154,16 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.99%83,000</t>
+          <t>1.00%45,400</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>83000</v>
+        <v>45400</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:54</t>
+          <t>2026-09-30 23:56:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1197,40 +1197,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>4062IBIDEN CO LTD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0%3305</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.90%106,000</t>
+          <t>0.98%166,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>106000</v>
+        <v>166000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:54</t>
+          <t>2026-09-30 23:56:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1260,40 +1260,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.16%5125</t>
+          <t>0%3305</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.86%60,000</t>
+          <t>0.93%106,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>60000</v>
+        <v>106000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:54</t>
+          <t>2026-09-30 23:56:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.79%130,000</t>
+          <t>0.75%130,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-30 23:16:54</t>
+          <t>2026-09-30 23:56:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.67%7,234</t>
+          <t>0.69%7,234</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1423,195 +1423,6 @@
         </is>
       </c>
       <c r="M16" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-09-30 23:16:54</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>7769鴻勁</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-1.43%5505</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-1.43%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>5505</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.61%41,000</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0.61%</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>41000</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-09-30 23:16:56</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>3665貿聯-KY</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>+6.13%2595</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>+6.13%</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2595</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.58%94,000</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0.58%</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>94000</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-09-30 23:16:56</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>6920LASERTEC CORP</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.48%22,600</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.48%</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>22600</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>
